--- a/output/2026-10-07_04_Serbia_Mačvanski_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-07_04_Serbia_Mačvanski_Componentistica_Ventilazione_industriale.xlsx
@@ -506,7 +506,6 @@
           <t>Doming - oprema za grejanje i klimatizaciju</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Šabac, Mačvanski okrug (Pocerska 84)</t>
@@ -522,7 +521,6 @@
           <t>015/7760-300</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Verificato tramite directory planplus.rs (indirizzo e telefono confermati). Borderline: focus prevalentemente residenziale/commerciale, non chiaramente industriale.</t>
@@ -540,7 +538,6 @@
           <t>Energotech</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Šabac, Mačvanski okrug (Vlade Stanimirovića 2)</t>
@@ -556,7 +553,6 @@
           <t>015/341-700</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Verificato tramite planplus.rs. Borderline: descritta come ditta di installazioni termotecniche, verificare se opera anche come distributore di componenti o solo come installatore.</t>
@@ -574,7 +570,6 @@
           <t>Etaž - oprema za grejanje i klimatizaciju (filiale Šabac)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Šabac, Mačvanski okrug (Pop Lukina 9)</t>
@@ -590,7 +585,6 @@
           <t>015/349-850, 069/8276-283</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Verificato tramite planplus.rs. Filiale locale della catena nazionale Etaž d.o.o. (17 negozi + 4 ingrosso in Serbia); le filiali di Belgrado sono state scartate come duplicati.</t>
@@ -608,7 +602,6 @@
           <t>KTS Plus - grejanje i klimatizacija</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Loznica, Mačvanski okrug (Ivana Cankara 1A)</t>
@@ -624,7 +617,6 @@
           <t>015/876-393</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Verificato tramite planplus.rs. Borderline: prevalentemente residenziale-commerciale.</t>
@@ -642,7 +634,6 @@
           <t>Industrijska oprema (tehnološka rešenja za industrijski vazduh)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Beograd - Zemun (Banatska 28V) - area allargata, fuori Mačva</t>
@@ -658,10 +649,9 @@
           <t>011/3077-086</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Verificato tramite planplus.rs (indirizzo confermato). Area allargata a tutta la Serbia per scarsità di risultati locali in Mačva.</t>
+          <t>Verificato tramite planplus.rs (indirizzo confermato). Area allargata a tutta la Serbia per scarsità di risultati locali in Mačva. [DUPLICATO — vedi anche: 2026-10-06_21_Serbia_Grad_Beograd_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -676,7 +666,6 @@
           <t>Ecotip Tedex</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Beograd - Zemun (Taška Načića 5B) - area allargata, fuori Mačva</t>
@@ -692,10 +681,9 @@
           <t>011/2450-976</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Verificato tramite planplus.rs; collegata al gruppo Ecotip (sede principale Skopje, Macedonia del Nord), attiva nella filtrazione aria/liquidi. Area allargata.</t>
+          <t>Verificato tramite planplus.rs; collegata al gruppo Ecotip (sede principale Skopje, Macedonia del Nord), attiva nella filtrazione aria/liquidi. Area allargata. [DUPLICATO — vedi anche: 2026-10-06_21_Serbia_Grad_Beograd_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -737,7 +725,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Verificato tramite sito ufficiale Systemair. Filiale commerciale del gruppo internazionale Systemair. Area allargata a tutta la Serbia.</t>
+          <t>Verificato tramite sito ufficiale Systemair. Filiale commerciale del gruppo internazionale Systemair. Area allargata a tutta la Serbia. [DUPLICATO — vedi anche: 2026-10-06_23_Serbia_Grad_Beograd_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -752,7 +740,6 @@
           <t>YAFI FILTERTECH SERBIA d.o.o.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Serbia (sede esatta non reperita) - area allargata</t>
@@ -763,8 +750,6 @@
           <t>Produzione/distribuzione filtri per aria in ambienti chiusi (air filtration)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Esistenza confermata tramite elenco espositori fiera Filtech 2024 (filtech.de): produttore leader di filtrazione aria in Sud-Est Europa. Sede esatta e contatti non reperiti con fonti verificabili, lasciati vuoti.</t>
@@ -802,7 +787,6 @@
           <t>+381 63 59 33 22</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Verificato tramite hainzl.at, bizi.si e industrial.filtrationgroup.com (Joint Venture con rappresentante Danfoss Vladex). Email non reperita con fonte affidabile, lasciata vuota.</t>
@@ -840,7 +824,6 @@
           <t>+381 60 6606 125 (Tamara Šparović Kocić)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Verificato tramite sito ufficiale e web search (indirizzo confermato). Produttore con 30 anni di esperienza, attivo in oltre 20 paesi, clienti come Pfizer/Zoetis. Email non reperita.</t>
@@ -858,7 +841,6 @@
           <t>Delta Filter d.o.o.</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Arilje, Zlatiborski okrug (Viktora Zevnika 1) - area allargata, fuori Mačva</t>
@@ -869,8 +851,6 @@
           <t>Distributore/rappresentante filtri Donaldson (aria, olio, carburante, idraulici) e compressori RENNER</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Verificato tramite ekapija.com (indirizzo confermato). Telefono/email non reperiti con fonte affidabile.</t>

--- a/output/2026-10-07_04_Serbia_Mačvanski_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-07_04_Serbia_Mačvanski_Componentistica_Ventilazione_industriale.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
